--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N93_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N93_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.51346209640753</v>
+        <v>6.258437590666224</v>
       </c>
       <c r="D2" t="n">
-        <v>38.35310349212984</v>
+        <v>6.232379317471099</v>
       </c>
       <c r="E2" t="n">
-        <v>19.33263027443788</v>
+        <v>3.141552419596155</v>
       </c>
       <c r="F2" t="n">
-        <v>13.38955911794467</v>
+        <v>2.175803356666009</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.65492831295305</v>
+        <v>8.068925850854871</v>
       </c>
       <c r="D3" t="n">
-        <v>29.38542421196933</v>
+        <v>4.775131434445017</v>
       </c>
       <c r="E3" t="n">
-        <v>19.33263027443788</v>
+        <v>3.141552419596155</v>
       </c>
       <c r="F3" t="n">
-        <v>13.38955911794467</v>
+        <v>2.175803356666009</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>71.16718427965067</v>
+        <v>11.56466744544323</v>
       </c>
       <c r="D4" t="n">
-        <v>34.44684557228172</v>
+        <v>5.597612405495781</v>
       </c>
       <c r="E4" t="n">
-        <v>19.33263027443788</v>
+        <v>3.141552419596155</v>
       </c>
       <c r="F4" t="n">
-        <v>13.38955911794467</v>
+        <v>2.175803356666009</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>60.53592223093212</v>
+        <v>9.83708736252647</v>
       </c>
       <c r="D5" t="n">
-        <v>19.8916082550289</v>
+        <v>3.232386341442197</v>
       </c>
       <c r="E5" t="n">
-        <v>19.33263027443788</v>
+        <v>3.141552419596155</v>
       </c>
       <c r="F5" t="n">
-        <v>13.38955911794467</v>
+        <v>2.175803356666009</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>57.67735074960178</v>
+        <v>9.372569496810289</v>
       </c>
       <c r="D6" t="n">
-        <v>57.99169985869504</v>
+        <v>9.423651227037944</v>
       </c>
       <c r="E6" t="n">
-        <v>19.33263027443788</v>
+        <v>3.141552419596155</v>
       </c>
       <c r="F6" t="n">
-        <v>13.38955911794467</v>
+        <v>2.175803356666009</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.07751757154159</v>
+        <v>4.725096605375509</v>
       </c>
       <c r="D7" t="n">
-        <v>28.24304180556405</v>
+        <v>4.589494293404159</v>
       </c>
       <c r="E7" t="n">
-        <v>19.33263027443788</v>
+        <v>3.141552419596155</v>
       </c>
       <c r="F7" t="n">
-        <v>13.38955911794467</v>
+        <v>2.175803356666009</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>10.57925483077483</v>
+        <v>1.719128910000911</v>
       </c>
       <c r="D8" t="n">
-        <v>9.935644391706965</v>
+        <v>1.614542213652382</v>
       </c>
       <c r="E8" t="n">
-        <v>19.33263027443788</v>
+        <v>3.141552419596155</v>
       </c>
       <c r="F8" t="n">
-        <v>13.38955911794467</v>
+        <v>2.175803356666009</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.88503221637646</v>
+        <v>3.881317735161175</v>
       </c>
       <c r="D9" t="n">
-        <v>22.71633014658833</v>
+        <v>3.691403648820604</v>
       </c>
       <c r="E9" t="n">
-        <v>19.33263027443788</v>
+        <v>3.141552419596155</v>
       </c>
       <c r="F9" t="n">
-        <v>13.38955911794467</v>
+        <v>2.175803356666009</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
